--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3599" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="660">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profil Body weight based on the FHIR profil BodyWeightMeas.
+    <t>French profile of body weight based on the FHIR profil BodyWeightMeas.
 Profil français Body weight basé sur le profil HL7 BodyWeightMeas de Vital Signs.</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodyweight</t>
+    <t>http://hl7.org/fhir/StructureDefinition/bodyweight|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,6 +488,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-weight|2.2.0</t>
+  </si>
+  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -510,7 +513,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -534,7 +537,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -577,7 +580,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -653,7 +656,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -714,7 +717,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -743,7 +746,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -823,7 +826,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1078,7 +1081,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1172,7 +1175,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1203,7 +1206,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1226,7 +1229,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -1321,7 +1324,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1565,7 +1568,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1597,7 +1600,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1653,7 +1656,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1683,7 +1686,10 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-weight-measurement-method</t>
+    <t>Methods for simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1695,7 +1701,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1723,7 +1729,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1803,7 +1809,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1853,7 +1859,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1886,7 +1892,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1923,7 +1929,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1945,7 +1951,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2394,17 +2400,17 @@
   <dimension ref="A1:AP93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.51171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.9921875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.57421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="226.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="222.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2413,28 +2419,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.33984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3691,7 +3697,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3765,10 +3771,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3791,16 +3797,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3826,13 +3832,13 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>83</v>
@@ -3850,7 +3856,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3885,10 +3891,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3911,16 +3917,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3946,13 +3952,13 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>83</v>
@@ -3970,7 +3976,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4005,10 +4011,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4034,13 +4040,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4090,7 +4096,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4125,10 +4131,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4151,16 +4157,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4186,13 +4192,13 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -4210,7 +4216,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4245,14 +4251,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4271,16 +4277,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4330,7 +4336,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4354,7 +4360,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4365,14 +4371,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4391,16 +4397,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4450,7 +4456,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4474,7 +4480,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4485,10 +4491,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4514,10 +4520,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4566,7 +4572,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4601,13 +4607,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4629,13 +4635,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4686,7 +4692,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4721,10 +4727,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4750,16 +4756,16 @@
         <v>115</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4808,7 +4814,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4832,7 +4838,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4843,10 +4849,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4869,17 +4875,17 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -4928,7 +4934,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4943,19 +4949,19 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4963,14 +4969,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4989,17 +4995,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5048,7 +5054,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5063,16 +5069,16 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5083,14 +5089,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5109,16 +5115,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5168,7 +5174,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5183,16 +5189,16 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5201,12 +5207,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5229,19 +5235,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5266,11 +5272,11 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5288,7 +5294,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>94</v>
@@ -5303,19 +5309,19 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
@@ -5323,10 +5329,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5349,19 +5355,19 @@
         <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5386,19 +5392,19 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5408,7 +5414,7 @@
         <v>121</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5432,24 +5438,24 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>83</v>
@@ -5471,19 +5477,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5508,13 +5514,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5532,7 +5538,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5556,10 +5562,10 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5567,10 +5573,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5685,10 +5691,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5803,12 +5809,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5831,19 +5837,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5892,7 +5898,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5913,10 +5919,10 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5927,10 +5933,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6045,10 +6051,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6163,12 +6169,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6194,23 +6200,23 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>83</v>
@@ -6252,7 +6258,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6273,10 +6279,10 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6287,10 +6293,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6316,13 +6322,13 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6372,7 +6378,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6393,10 +6399,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6405,12 +6411,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6433,24 +6439,24 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6492,7 +6498,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6513,10 +6519,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6527,10 +6533,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6556,14 +6562,14 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6612,7 +6618,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6633,10 +6639,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6647,10 +6653,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6673,19 +6679,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6734,7 +6740,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6755,10 +6761,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6769,10 +6775,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6798,16 +6804,16 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6856,7 +6862,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6877,10 +6883,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6889,16 +6895,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6917,19 +6923,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6954,13 +6960,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6978,7 +6984,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>94</v>
@@ -6993,30 +6999,30 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7131,10 +7137,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7251,10 +7257,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7277,19 +7283,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7326,7 +7332,7 @@
         <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7336,7 +7342,7 @@
         <v>121</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7357,10 +7363,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7371,13 +7377,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>83</v>
@@ -7399,19 +7405,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7460,7 +7466,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7481,10 +7487,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7495,10 +7501,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7613,10 +7619,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7733,10 +7739,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7762,23 +7768,23 @@
         <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>83</v>
@@ -7820,7 +7826,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7841,10 +7847,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7855,10 +7861,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7884,13 +7890,13 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7940,7 +7946,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7961,10 +7967,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7975,10 +7981,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8001,24 +8007,24 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -8060,7 +8066,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8081,10 +8087,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8095,10 +8101,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8124,14 +8130,14 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8180,7 +8186,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8201,10 +8207,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8215,10 +8221,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8241,19 +8247,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8302,7 +8308,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8323,10 +8329,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8337,10 +8343,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8366,16 +8372,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8424,7 +8430,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8445,10 +8451,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8457,12 +8463,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8485,19 +8491,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8546,7 +8552,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8561,19 +8567,19 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8581,10 +8587,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8607,16 +8613,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8666,7 +8672,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8687,13 +8693,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8701,14 +8707,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8727,19 +8733,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8788,7 +8794,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8803,34 +8809,34 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8849,19 +8855,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8910,7 +8916,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8919,25 +8925,25 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8945,10 +8951,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8974,13 +8980,13 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9030,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9051,13 +9057,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9065,10 +9071,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9091,17 +9097,17 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9150,7 +9156,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9165,19 +9171,19 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9185,10 +9191,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9211,19 +9217,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9260,17 +9266,17 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9279,7 +9285,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9288,30 +9294,30 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>83</v>
@@ -9333,19 +9339,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9394,7 +9400,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9403,7 +9409,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9412,27 +9418,27 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9547,10 +9553,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9665,12 +9671,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9693,19 +9699,19 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9754,7 +9760,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9775,10 +9781,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9789,10 +9795,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9815,23 +9821,23 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="R62" t="s" s="2">
         <v>83</v>
@@ -9852,13 +9858,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9876,7 +9882,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9897,10 +9903,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9909,12 +9915,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9940,14 +9946,14 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9996,7 +10002,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10017,10 +10023,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10029,12 +10035,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10060,21 +10066,21 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>83</v>
@@ -10116,7 +10122,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10125,7 +10131,7 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -10137,10 +10143,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10149,12 +10155,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10177,19 +10183,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10214,13 +10220,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10238,7 +10244,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10259,10 +10265,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10271,12 +10277,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10299,19 +10305,19 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10336,13 +10342,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -10360,7 +10366,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10369,7 +10375,7 @@
         <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>106</v>
@@ -10381,10 +10387,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10395,14 +10401,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10421,19 +10427,19 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10458,13 +10464,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10482,7 +10488,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10500,27 +10506,27 @@
         <v>83</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10543,19 +10549,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10604,7 +10610,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10625,10 +10631,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10639,10 +10645,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10665,16 +10671,16 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10700,13 +10706,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10724,7 +10730,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10742,27 +10748,27 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10785,19 +10791,19 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10822,11 +10828,13 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10844,7 +10852,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10865,10 +10873,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10879,10 +10887,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10905,16 +10913,16 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10964,7 +10972,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10982,27 +10990,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11025,16 +11033,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11084,7 +11092,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11102,27 +11110,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11145,19 +11153,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11206,7 +11214,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11218,7 +11226,7 @@
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
@@ -11227,10 +11235,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11241,10 +11249,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11359,10 +11367,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11479,14 +11487,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11508,16 +11516,16 @@
         <v>115</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11566,7 +11574,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11590,7 +11598,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11601,10 +11609,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11627,13 +11635,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11684,7 +11692,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11693,7 +11701,7 @@
         <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -11705,10 +11713,10 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11719,10 +11727,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11745,13 +11753,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11802,7 +11810,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11811,7 +11819,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11823,10 +11831,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11837,10 +11845,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11863,19 +11871,19 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11900,13 +11908,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11924,7 +11932,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11942,13 +11950,13 @@
         <v>83</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11959,10 +11967,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11985,19 +11993,19 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12022,13 +12030,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12046,7 +12054,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12064,13 +12072,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12081,10 +12089,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12107,17 +12115,17 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12166,7 +12174,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12190,7 +12198,7 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12201,10 +12209,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12230,10 +12238,10 @@
         <v>108</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12284,7 +12292,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12305,10 +12313,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12319,10 +12327,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12345,16 +12353,16 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12404,7 +12412,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12425,10 +12433,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12439,10 +12447,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12465,16 +12473,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12524,7 +12532,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12545,10 +12553,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12557,12 +12565,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12585,19 +12593,19 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12646,7 +12654,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12658,7 +12666,7 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
@@ -12667,10 +12675,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12681,10 +12689,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12799,10 +12807,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12919,14 +12927,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12948,16 +12956,16 @@
         <v>115</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13006,7 +13014,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13030,7 +13038,7 @@
         <v>83</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13039,12 +13047,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13067,19 +13075,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13104,13 +13112,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13128,7 +13136,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>94</v>
@@ -13146,27 +13154,27 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13189,19 +13197,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13226,13 +13234,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13250,7 +13258,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13259,7 +13267,7 @@
         <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>106</v>
@@ -13268,27 +13276,27 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13311,19 +13319,19 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13348,13 +13356,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13372,7 +13380,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13381,7 +13389,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13393,10 +13401,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13407,14 +13415,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13433,19 +13441,19 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13470,13 +13478,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13494,7 +13502,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13512,27 +13520,27 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13558,16 +13566,16 @@
         <v>84</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13616,7 +13624,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13637,10 +13645,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13651,12 +13659,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP93">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3599" uniqueCount="658">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile of body weight based on the FHIR profil BodyWeightMeas.
+    <t>French profil Body weight based on the FHIR profil BodyWeightMeas.
 Profil français Body weight basé sur le profil HL7 BodyWeightMeas de Vital Signs.</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodyweight|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/bodyweight</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,9 +488,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-weight|2.2.0</t>
-  </si>
-  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -513,7 +510,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -537,7 +534,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -580,7 +577,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -656,7 +653,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
+    <t xml:space="preserve">Extension {workflow-supportingInfo}
 </t>
   </si>
   <si>
@@ -717,7 +714,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -746,7 +743,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -826,7 +823,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1081,7 +1078,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1175,7 +1172,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1206,7 +1203,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1229,7 +1226,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -1324,7 +1321,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|4.0.1|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
+    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1568,7 +1565,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t>obs-6
@@ -1600,7 +1597,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1656,7 +1653,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1686,10 +1683,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-weight-measurement-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1701,7 +1695,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1729,7 +1723,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1809,7 +1803,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1859,7 +1853,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1892,7 +1886,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1929,7 +1923,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
 </t>
   </si>
   <si>
@@ -1951,7 +1945,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
 </t>
   </si>
   <si>
@@ -2400,17 +2394,17 @@
   <dimension ref="A1:AP93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.51171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.9921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="222.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="226.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2419,28 +2413,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.33984375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3697,7 +3691,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3771,10 +3765,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3797,16 +3791,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3832,31 +3826,31 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3891,10 +3885,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3917,16 +3911,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3952,31 +3946,31 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4011,10 +4005,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4040,13 +4034,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4096,7 +4090,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4131,10 +4125,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4157,16 +4151,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4192,31 +4186,31 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4251,14 +4245,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4277,16 +4271,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4336,7 +4330,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4360,7 +4354,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4371,14 +4365,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4397,16 +4391,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4456,7 +4450,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4480,7 +4474,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4491,10 +4485,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4520,10 +4514,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4572,7 +4566,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4607,13 +4601,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4635,13 +4629,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4692,7 +4686,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4727,10 +4721,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4756,16 +4750,16 @@
         <v>115</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4814,7 +4808,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4838,7 +4832,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4849,10 +4843,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4875,17 +4869,17 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -4934,7 +4928,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4949,19 +4943,19 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4969,14 +4963,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4995,17 +4989,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5054,7 +5048,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5069,16 +5063,16 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5089,14 +5083,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5115,16 +5109,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5174,7 +5168,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5189,30 +5183,30 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AO23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>240</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5235,19 +5229,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5272,11 +5266,11 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5294,7 +5288,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>94</v>
@@ -5309,19 +5303,19 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
@@ -5329,10 +5323,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5355,19 +5349,19 @@
         <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5392,19 +5386,19 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5414,7 +5408,7 @@
         <v>121</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5438,24 +5432,24 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AP25" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
+      <c r="B26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>83</v>
@@ -5477,19 +5471,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5514,14 +5508,14 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
       </c>
@@ -5538,7 +5532,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5562,10 +5556,10 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5573,10 +5567,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5691,10 +5685,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5809,12 +5803,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5837,19 +5831,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5898,7 +5892,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5919,10 +5913,10 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5933,10 +5927,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6051,10 +6045,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6169,12 +6163,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6200,65 +6194,65 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6279,10 +6273,10 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6293,10 +6287,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6322,13 +6316,13 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6378,7 +6372,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6399,24 +6393,24 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AO33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
+      <c r="B34" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6439,66 +6433,66 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6519,10 +6513,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6533,10 +6527,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6562,14 +6556,14 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6618,7 +6612,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6639,10 +6633,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6653,10 +6647,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6679,19 +6673,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6740,7 +6734,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6761,10 +6755,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6775,10 +6769,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6804,16 +6798,16 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6862,7 +6856,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6883,28 +6877,28 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6923,19 +6917,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6960,14 +6954,14 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>343</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6984,7 +6978,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>94</v>
@@ -6999,30 +6993,30 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7137,10 +7131,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7257,10 +7251,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7283,19 +7277,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7332,7 +7326,7 @@
         <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7342,7 +7336,7 @@
         <v>121</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7363,10 +7357,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7377,13 +7371,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>83</v>
@@ -7405,19 +7399,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7466,7 +7460,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7487,10 +7481,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7501,10 +7495,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7619,10 +7613,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7739,10 +7733,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7768,23 +7762,23 @@
         <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>83</v>
@@ -7826,7 +7820,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7847,10 +7841,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7861,10 +7855,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7890,13 +7884,13 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7946,7 +7940,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7967,10 +7961,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7981,10 +7975,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8007,24 +8001,24 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -8066,7 +8060,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8087,10 +8081,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8101,10 +8095,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8130,14 +8124,14 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8186,7 +8180,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8207,10 +8201,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8221,10 +8215,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8247,19 +8241,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8308,7 +8302,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8329,10 +8323,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8343,10 +8337,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8372,16 +8366,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8430,7 +8424,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8451,11 +8445,11 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AN50" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
@@ -8463,12 +8457,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8491,19 +8485,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8552,7 +8546,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8567,19 +8561,19 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8587,10 +8581,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8613,16 +8607,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8672,7 +8666,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8693,13 +8687,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8707,14 +8701,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8733,19 +8727,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8794,7 +8788,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8809,34 +8803,34 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AP53" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="B54" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8855,19 +8849,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8916,7 +8910,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8925,25 +8919,25 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AJ54" t="s" s="2">
+      <c r="AK54" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AK54" t="s" s="2">
+      <c r="AL54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8951,10 +8945,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8980,13 +8974,13 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9036,7 +9030,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9057,13 +9051,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9071,10 +9065,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9097,17 +9091,17 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9156,7 +9150,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9171,19 +9165,19 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9191,10 +9185,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9217,19 +9211,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9266,17 +9260,17 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9285,7 +9279,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9294,30 +9288,30 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP57" t="s" s="2">
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
         <v>440</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
+      <c r="B58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C58" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>83</v>
@@ -9339,19 +9333,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9400,7 +9394,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9409,7 +9403,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9418,27 +9412,27 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>440</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9553,10 +9547,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9671,12 +9665,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9699,19 +9693,19 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9760,7 +9754,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9781,10 +9775,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9795,10 +9789,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9821,68 +9815,68 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q62" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="P62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q62" t="s" s="2">
+      <c r="R62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Y62" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="R62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y62" t="s" s="2">
+      <c r="Z62" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z62" t="s" s="2">
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9903,24 +9897,24 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
+      <c r="B63" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9946,14 +9940,14 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10002,7 +9996,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10023,24 +10017,24 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
+      <c r="B64" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10066,63 +10060,63 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10131,7 +10125,7 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -10143,24 +10137,24 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AO64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
+      <c r="B65" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10183,19 +10177,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10220,31 +10214,31 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Z65" t="s" s="2">
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10265,24 +10259,24 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AO65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="B66" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10305,19 +10299,19 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10342,14 +10336,14 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
       </c>
@@ -10366,7 +10360,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10375,7 +10369,7 @@
         <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>106</v>
@@ -10387,10 +10381,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10401,14 +10395,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10427,19 +10421,19 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10464,14 +10458,14 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
       </c>
@@ -10488,7 +10482,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10506,27 +10500,27 @@
         <v>83</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10549,19 +10543,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10610,7 +10604,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10631,10 +10625,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10645,10 +10639,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10671,16 +10665,16 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10706,14 +10700,14 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10730,7 +10724,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10748,27 +10742,27 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>532</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10791,19 +10785,19 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10828,13 +10822,11 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10852,7 +10844,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10873,10 +10865,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10887,10 +10879,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10913,16 +10905,16 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10972,7 +10964,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10990,27 +10982,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11033,16 +11025,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11092,7 +11084,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11110,27 +11102,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11153,19 +11145,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11214,7 +11206,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11226,19 +11218,19 @@
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11249,10 +11241,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11367,10 +11359,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11487,14 +11479,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11516,16 +11508,16 @@
         <v>115</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11574,7 +11566,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11598,7 +11590,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11609,10 +11601,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11635,13 +11627,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11692,7 +11684,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11701,7 +11693,7 @@
         <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -11713,10 +11705,10 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11727,10 +11719,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11753,13 +11745,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11810,7 +11802,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11819,7 +11811,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11831,10 +11823,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11845,10 +11837,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11871,19 +11863,19 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11908,13 +11900,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11932,7 +11924,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11950,13 +11942,13 @@
         <v>83</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11967,10 +11959,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11993,19 +11985,19 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12030,13 +12022,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12054,7 +12046,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12072,13 +12064,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12089,10 +12081,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12115,17 +12107,17 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12174,7 +12166,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12198,7 +12190,7 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12209,10 +12201,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12238,10 +12230,10 @@
         <v>108</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12292,7 +12284,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12313,10 +12305,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12327,10 +12319,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12353,16 +12345,16 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12412,7 +12404,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12433,10 +12425,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12447,10 +12439,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12473,16 +12465,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12532,7 +12524,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12553,10 +12545,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12565,12 +12557,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12593,19 +12585,19 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O85" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12654,7 +12646,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12666,19 +12658,19 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12689,10 +12681,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12807,10 +12799,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12927,14 +12919,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12956,16 +12948,16 @@
         <v>115</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13014,7 +13006,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13038,7 +13030,7 @@
         <v>83</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13047,12 +13039,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13075,19 +13067,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13112,14 +13104,14 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="Z89" t="s" s="2">
-        <v>343</v>
-      </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13136,7 +13128,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>94</v>
@@ -13154,27 +13146,27 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AO89" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13197,19 +13189,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>646</v>
-      </c>
       <c r="O90" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13234,13 +13226,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13258,7 +13250,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13267,7 +13259,7 @@
         <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>106</v>
@@ -13276,27 +13268,27 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AO90" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>440</v>
-      </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13319,19 +13311,19 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>654</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13356,14 +13348,14 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
       </c>
@@ -13380,7 +13372,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13389,7 +13381,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13401,10 +13393,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13415,14 +13407,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13441,19 +13433,19 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13478,14 +13470,14 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13502,7 +13494,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13520,27 +13512,27 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13566,16 +13558,16 @@
         <v>84</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13624,7 +13616,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13645,10 +13637,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13659,12 +13651,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP93">
-    <filterColumn colId="7">
+    <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="27">
+    <filterColumn colId="26">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3599" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="660">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profil Body weight based on the FHIR profil BodyWeightMeas.
+    <t>French profile of body weight based on the FHIR profil BodyWeightMeas.
 Profil français Body weight basé sur le profil HL7 BodyWeightMeas de Vital Signs.</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodyweight</t>
+    <t>http://hl7.org/fhir/StructureDefinition/bodyweight|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,6 +488,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-weight|2.2.0</t>
+  </si>
+  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -510,7 +513,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -534,7 +537,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -577,7 +580,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -653,7 +656,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -714,7 +717,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -743,7 +746,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -823,7 +826,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1078,7 +1081,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1172,7 +1175,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1203,7 +1206,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1226,7 +1229,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -1321,7 +1324,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1565,7 +1568,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1597,7 +1600,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1653,7 +1656,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1683,7 +1686,10 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-weight-measurement-method</t>
+    <t>Methods for simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1695,7 +1701,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1723,7 +1729,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1803,7 +1809,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1853,7 +1859,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1886,7 +1892,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1923,7 +1929,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1945,7 +1951,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2394,17 +2400,17 @@
   <dimension ref="A1:AP93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.51171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.9921875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.57421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="226.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="222.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2413,28 +2419,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.33984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3691,7 +3697,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3765,10 +3771,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3791,16 +3797,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3826,13 +3832,13 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>83</v>
@@ -3850,7 +3856,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3885,10 +3891,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3911,16 +3917,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3946,13 +3952,13 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>83</v>
@@ -3970,7 +3976,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4005,10 +4011,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4034,13 +4040,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4090,7 +4096,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4125,10 +4131,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4151,16 +4157,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4186,13 +4192,13 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -4210,7 +4216,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4245,14 +4251,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4271,16 +4277,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4330,7 +4336,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4354,7 +4360,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4365,14 +4371,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4391,16 +4397,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4450,7 +4456,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4474,7 +4480,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4485,10 +4491,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4514,10 +4520,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4566,7 +4572,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4601,13 +4607,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4629,13 +4635,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4686,7 +4692,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4721,10 +4727,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4750,16 +4756,16 @@
         <v>115</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4808,7 +4814,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4832,7 +4838,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4843,10 +4849,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4869,17 +4875,17 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -4928,7 +4934,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4943,19 +4949,19 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4963,14 +4969,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4989,17 +4995,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5048,7 +5054,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5063,16 +5069,16 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5083,14 +5089,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5109,16 +5115,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5168,7 +5174,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5183,16 +5189,16 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5201,12 +5207,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5229,19 +5235,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5266,11 +5272,11 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5288,7 +5294,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>94</v>
@@ -5303,19 +5309,19 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
@@ -5323,10 +5329,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5349,19 +5355,19 @@
         <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5386,19 +5392,19 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5408,7 +5414,7 @@
         <v>121</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5432,24 +5438,24 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>83</v>
@@ -5471,19 +5477,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5508,13 +5514,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5532,7 +5538,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5556,10 +5562,10 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5567,10 +5573,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5685,10 +5691,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5803,12 +5809,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5831,19 +5837,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5892,7 +5898,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5913,10 +5919,10 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5927,10 +5933,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6045,10 +6051,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6163,12 +6169,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6194,23 +6200,23 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>83</v>
@@ -6252,7 +6258,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6273,10 +6279,10 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6287,10 +6293,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6316,13 +6322,13 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6372,7 +6378,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6393,10 +6399,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6405,12 +6411,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6433,24 +6439,24 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6492,7 +6498,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6513,10 +6519,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6527,10 +6533,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6556,14 +6562,14 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6612,7 +6618,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6633,10 +6639,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6647,10 +6653,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6673,19 +6679,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6734,7 +6740,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6755,10 +6761,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6769,10 +6775,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6798,16 +6804,16 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6856,7 +6862,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6877,10 +6883,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6889,16 +6895,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6917,19 +6923,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6954,13 +6960,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6978,7 +6984,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>94</v>
@@ -6993,30 +6999,30 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7131,10 +7137,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7251,10 +7257,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7277,19 +7283,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7326,7 +7332,7 @@
         <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7336,7 +7342,7 @@
         <v>121</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7357,10 +7363,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7371,13 +7377,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>83</v>
@@ -7399,19 +7405,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7460,7 +7466,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7481,10 +7487,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7495,10 +7501,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7613,10 +7619,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7733,10 +7739,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7762,23 +7768,23 @@
         <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>83</v>
@@ -7820,7 +7826,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7841,10 +7847,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7855,10 +7861,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7884,13 +7890,13 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7940,7 +7946,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7961,10 +7967,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7975,10 +7981,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8001,24 +8007,24 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -8060,7 +8066,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8081,10 +8087,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8095,10 +8101,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8124,14 +8130,14 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8180,7 +8186,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8201,10 +8207,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8215,10 +8221,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8241,19 +8247,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8302,7 +8308,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8323,10 +8329,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8337,10 +8343,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8366,16 +8372,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8424,7 +8430,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8445,10 +8451,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8457,12 +8463,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8485,19 +8491,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8546,7 +8552,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8561,19 +8567,19 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8581,10 +8587,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8607,16 +8613,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8666,7 +8672,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8687,13 +8693,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8701,14 +8707,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8727,19 +8733,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8788,7 +8794,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8803,34 +8809,34 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8849,19 +8855,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8910,7 +8916,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8919,25 +8925,25 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8945,10 +8951,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8974,13 +8980,13 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9030,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9051,13 +9057,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9065,10 +9071,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9091,17 +9097,17 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9150,7 +9156,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9165,19 +9171,19 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9185,10 +9191,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9211,19 +9217,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9260,17 +9266,17 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9279,7 +9285,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9288,30 +9294,30 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>83</v>
@@ -9333,19 +9339,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9394,7 +9400,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9403,7 +9409,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9412,27 +9418,27 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9547,10 +9553,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9665,12 +9671,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9693,19 +9699,19 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9754,7 +9760,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9775,10 +9781,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9789,10 +9795,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9815,23 +9821,23 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="R62" t="s" s="2">
         <v>83</v>
@@ -9852,13 +9858,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9876,7 +9882,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9897,10 +9903,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9909,12 +9915,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9940,14 +9946,14 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9996,7 +10002,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10017,10 +10023,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10029,12 +10035,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10060,21 +10066,21 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>83</v>
@@ -10116,7 +10122,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10125,7 +10131,7 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -10137,10 +10143,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10149,12 +10155,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10177,19 +10183,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10214,13 +10220,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10238,7 +10244,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10259,10 +10265,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10271,12 +10277,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10299,19 +10305,19 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10336,13 +10342,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -10360,7 +10366,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10369,7 +10375,7 @@
         <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>106</v>
@@ -10381,10 +10387,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10395,14 +10401,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10421,19 +10427,19 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10458,13 +10464,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10482,7 +10488,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10500,27 +10506,27 @@
         <v>83</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10543,19 +10549,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10604,7 +10610,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10625,10 +10631,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10639,10 +10645,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10665,16 +10671,16 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10700,13 +10706,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10724,7 +10730,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10742,27 +10748,27 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10785,19 +10791,19 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10822,11 +10828,13 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10844,7 +10852,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10865,10 +10873,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10879,10 +10887,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10905,16 +10913,16 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10964,7 +10972,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10982,27 +10990,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11025,16 +11033,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11084,7 +11092,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11102,27 +11110,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11145,19 +11153,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11206,7 +11214,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11218,7 +11226,7 @@
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
@@ -11227,10 +11235,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11241,10 +11249,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11359,10 +11367,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11479,14 +11487,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11508,16 +11516,16 @@
         <v>115</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11566,7 +11574,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11590,7 +11598,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11601,10 +11609,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11627,13 +11635,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11684,7 +11692,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11693,7 +11701,7 @@
         <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -11705,10 +11713,10 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11719,10 +11727,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11745,13 +11753,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11802,7 +11810,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11811,7 +11819,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11823,10 +11831,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11837,10 +11845,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11863,19 +11871,19 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11900,13 +11908,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11924,7 +11932,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11942,13 +11950,13 @@
         <v>83</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11959,10 +11967,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11985,19 +11993,19 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12022,13 +12030,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12046,7 +12054,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12064,13 +12072,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12081,10 +12089,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12107,17 +12115,17 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12166,7 +12174,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12190,7 +12198,7 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12201,10 +12209,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12230,10 +12238,10 @@
         <v>108</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12284,7 +12292,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12305,10 +12313,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12319,10 +12327,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12345,16 +12353,16 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12404,7 +12412,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12425,10 +12433,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12439,10 +12447,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12465,16 +12473,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12524,7 +12532,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12545,10 +12553,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12557,12 +12565,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12585,19 +12593,19 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12646,7 +12654,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12658,7 +12666,7 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
@@ -12667,10 +12675,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12681,10 +12689,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12799,10 +12807,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12919,14 +12927,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12948,16 +12956,16 @@
         <v>115</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13006,7 +13014,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13030,7 +13038,7 @@
         <v>83</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13039,12 +13047,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13067,19 +13075,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13104,13 +13112,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13128,7 +13136,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>94</v>
@@ -13146,27 +13154,27 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13189,19 +13197,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13226,13 +13234,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13250,7 +13258,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13259,7 +13267,7 @@
         <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>106</v>
@@ -13268,27 +13276,27 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13311,19 +13319,19 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13348,13 +13356,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13372,7 +13380,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13381,7 +13389,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13393,10 +13401,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13407,14 +13415,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13433,19 +13441,19 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13470,13 +13478,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13494,7 +13502,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13512,27 +13520,27 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13558,16 +13566,16 @@
         <v>84</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13616,7 +13624,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13637,10 +13645,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13651,12 +13659,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP93">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
